--- a/ResourcesTH/productPrice.xlsx
+++ b/ResourcesTH/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="51">
   <si>
     <t>Code*</t>
   </si>
@@ -142,6 +142,36 @@
   </si>
   <si>
     <t>2025-10-28</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>2025-11-03</t>
+  </si>
+  <si>
+    <t>2025-11-04</t>
+  </si>
+  <si>
+    <t>2025-11-10</t>
+  </si>
+  <si>
+    <t>2025-11-17</t>
+  </si>
+  <si>
+    <t>2025-11-18</t>
+  </si>
+  <si>
+    <t>2025-11-19</t>
+  </si>
+  <si>
+    <t>2025-11-20</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>2025-12-16</t>
   </si>
 </sst>
 </file>
@@ -557,19 +587,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>6641.0</v>
+        <v>7961.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>6482.0</v>
+        <v>9162.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>8744.0</v>
+        <v>2908.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>1994.0</v>
+        <v>8138.0</v>
       </c>
       <c r="N2" s="1">
         <v>0</v>

--- a/ResourcesTH/productPrice.xlsx
+++ b/ResourcesTH/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="51">
   <si>
     <t>Code*</t>
   </si>
@@ -590,16 +590,16 @@
         <v>50</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>7961.0</v>
+        <v>1984.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>9162.0</v>
+        <v>3672.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>2908.0</v>
+        <v>9214.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>8138.0</v>
+        <v>3979.0</v>
       </c>
       <c r="N2" s="1">
         <v>0</v>
